--- a/batch_bot/data/sample_data.xlsx
+++ b/batch_bot/data/sample_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,6 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>6</t>
@@ -552,7 +551,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -582,7 +581,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -622,7 +621,6 @@
           <t>Referral</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>7</t>
@@ -635,7 +633,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -665,7 +663,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -705,7 +703,6 @@
           <t>Yelp</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>8</t>
@@ -718,7 +715,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -748,7 +745,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -805,7 +802,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -835,7 +832,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -875,7 +872,6 @@
           <t>Yahoo</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>10</t>
@@ -888,7 +884,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -918,7 +914,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/batch_bot/data/sample_data.xlsx
+++ b/batch_bot/data/sample_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GITHUB REPOS\BATCH-AUTOMATION-AND-DATA-INTEGRATION-BOT\batch_bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC843A4B-C395-407A-88D0-CEC772D8371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8B7CC9-6EF7-4AAF-AC04-FE108B98EC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,37 +154,37 @@
     <t>Looking for advice on a personal injury case after a car accident.</t>
   </si>
   <si>
+    <t>Carol</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>5550303</t>
+  </si>
+  <si>
+    <t>carol.williams@example.com</t>
+  </si>
+  <si>
+    <t>Yelp</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Need consultation for a real-estate transaction and title issues.</t>
+  </si>
+  <si>
     <t>Pending</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>Williams</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>5550303</t>
-  </si>
-  <si>
-    <t>carol.williams@example.com</t>
-  </si>
-  <si>
-    <t>Yelp</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Need consultation for a real-estate transaction and title issues.</t>
   </si>
   <si>
     <t>David</t>
@@ -681,7 +681,7 @@
         <v>30</v>
       </c>
       <c r="Q2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -731,42 +731,42 @@
         <v>30</v>
       </c>
       <c r="Q3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>46</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>47</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
       <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" t="s">
         <v>50</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>51</v>
-      </c>
-      <c r="J4" t="s">
-        <v>52</v>
       </c>
       <c r="K4" t="s">
         <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M4" t="s">
         <v>27</v>
@@ -775,13 +775,13 @@
         <v>28</v>
       </c>
       <c r="O4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P4" t="s">
         <v>30</v>
       </c>
       <c r="Q4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -834,7 +834,7 @@
         <v>30</v>
       </c>
       <c r="Q5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -884,7 +884,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
